--- a/Breakthrough therapy analysis.xlsx
+++ b/Breakthrough therapy analysis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malap\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malap\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B11DAE-0B4C-4E55-98CA-0F620072F59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95B5C1F-766E-49D3-A4F8-3873A7848CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23F0A483-56FA-4297-93B8-4EC0AE1483F6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="261">
   <si>
     <t>Drug Name</t>
   </si>
@@ -705,6 +705,120 @@
   </si>
   <si>
     <t>NEUROCRINE BIOSCIENCES INC</t>
+  </si>
+  <si>
+    <t>JOURNAVX</t>
+  </si>
+  <si>
+    <t>VYKAT XR</t>
+  </si>
+  <si>
+    <t>PENPULIMAB</t>
+  </si>
+  <si>
+    <t>AVUTOMETINIB</t>
+  </si>
+  <si>
+    <t>TELISOTUZUMAB</t>
+  </si>
+  <si>
+    <t>MAVYRET</t>
+  </si>
+  <si>
+    <t>IBTROZI</t>
+  </si>
+  <si>
+    <t>YEZTUGO</t>
+  </si>
+  <si>
+    <t>DATROWAY</t>
+  </si>
+  <si>
+    <t>ZEGFROVY</t>
+  </si>
+  <si>
+    <t>HERNEXEOS</t>
+  </si>
+  <si>
+    <t>BRINSOPRI</t>
+  </si>
+  <si>
+    <t>WEGOVY</t>
+  </si>
+  <si>
+    <t>INLEXZO</t>
+  </si>
+  <si>
+    <t>JASCAYD</t>
+  </si>
+  <si>
+    <t>GAZYVA</t>
+  </si>
+  <si>
+    <t>KYGEVI</t>
+  </si>
+  <si>
+    <t>KOMZFITI</t>
+  </si>
+  <si>
+    <t>REDEMPLO</t>
+  </si>
+  <si>
+    <t>HYRNUO</t>
+  </si>
+  <si>
+    <t>VOXZACT</t>
+  </si>
+  <si>
+    <t>MYQORZO</t>
+  </si>
+  <si>
+    <t>YARTEMLA</t>
+  </si>
+  <si>
+    <t>VERTEX PHARMACEUTICALS INC</t>
+  </si>
+  <si>
+    <t>SOLENO THERAPEUTICS INC</t>
+  </si>
+  <si>
+    <t>AKESO BIOPHARMA CO LTD</t>
+  </si>
+  <si>
+    <t>VERASTEM INC</t>
+  </si>
+  <si>
+    <t>ABBVIE INC</t>
+  </si>
+  <si>
+    <t>NUVATION BIO INC</t>
+  </si>
+  <si>
+    <t>DIZAL (JIANGSU) PHARMACEUTICAL CO LTD</t>
+  </si>
+  <si>
+    <t>INSMED INC</t>
+  </si>
+  <si>
+    <t>UCB INC</t>
+  </si>
+  <si>
+    <t>KURA ONCOLOGY INC</t>
+  </si>
+  <si>
+    <t>ARROWHEAD PHARMACEUTICALS INC</t>
+  </si>
+  <si>
+    <t>BAYER HEALTHCARE PHARMACEUTICALS INC</t>
+  </si>
+  <si>
+    <t>OTSUKA PHARMACEUTICAL COMPANY LTD</t>
+  </si>
+  <si>
+    <t>CYTOKINETICS INC</t>
+  </si>
+  <si>
+    <t>OMEROS CORPORATION</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF12821-A0BF-482D-BCD5-E96B7B57EBC4}">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" bestFit="1" customWidth="1"/>
@@ -4004,6 +4118,746 @@
         <v>41</v>
       </c>
     </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="3">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>59</v>
+      </c>
+      <c r="C146" s="2">
+        <v>45673</v>
+      </c>
+      <c r="D146" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E146" t="s">
+        <v>86</v>
+      </c>
+      <c r="F146" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="3">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>28</v>
+      </c>
+      <c r="C147" s="2">
+        <v>45674</v>
+      </c>
+      <c r="D147" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E147" t="s">
+        <v>115</v>
+      </c>
+      <c r="F147" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="3">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>48</v>
+      </c>
+      <c r="C148" s="2">
+        <v>45684</v>
+      </c>
+      <c r="D148" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E148" t="s">
+        <v>75</v>
+      </c>
+      <c r="F148" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="3">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>223</v>
+      </c>
+      <c r="C149" s="2">
+        <v>45687</v>
+      </c>
+      <c r="D149" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E149" t="s">
+        <v>246</v>
+      </c>
+      <c r="F149" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="3">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>183</v>
+      </c>
+      <c r="C150" s="2">
+        <v>45736</v>
+      </c>
+      <c r="D150" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E150" t="s">
+        <v>96</v>
+      </c>
+      <c r="F150" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="3">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>224</v>
+      </c>
+      <c r="C151" s="2">
+        <v>45742</v>
+      </c>
+      <c r="D151" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E151" t="s">
+        <v>247</v>
+      </c>
+      <c r="F151" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="3">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>25</v>
+      </c>
+      <c r="C152" s="2">
+        <v>45750</v>
+      </c>
+      <c r="D152" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E152" t="s">
+        <v>100</v>
+      </c>
+      <c r="F152" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="3">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153" s="2">
+        <v>45755</v>
+      </c>
+      <c r="D153" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E153" t="s">
+        <v>98</v>
+      </c>
+      <c r="F153" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="3">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" s="2">
+        <v>45755</v>
+      </c>
+      <c r="D154" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E154" t="s">
+        <v>98</v>
+      </c>
+      <c r="F154" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="3">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>225</v>
+      </c>
+      <c r="C155" s="2">
+        <v>45770</v>
+      </c>
+      <c r="D155" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E155" t="s">
+        <v>248</v>
+      </c>
+      <c r="F155" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="3">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>226</v>
+      </c>
+      <c r="C156" s="2">
+        <v>45785</v>
+      </c>
+      <c r="D156" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E156" t="s">
+        <v>249</v>
+      </c>
+      <c r="F156" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="3">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>227</v>
+      </c>
+      <c r="C157" s="2">
+        <v>45791</v>
+      </c>
+      <c r="D157" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E157" t="s">
+        <v>250</v>
+      </c>
+      <c r="F157" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="3">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>228</v>
+      </c>
+      <c r="C158" s="2">
+        <v>45818</v>
+      </c>
+      <c r="D158" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E158" t="s">
+        <v>250</v>
+      </c>
+      <c r="F158" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="3">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>228</v>
+      </c>
+      <c r="C159" s="2">
+        <v>45818</v>
+      </c>
+      <c r="D159" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E159" t="s">
+        <v>250</v>
+      </c>
+      <c r="F159" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="3">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>229</v>
+      </c>
+      <c r="C160" s="2">
+        <v>45819</v>
+      </c>
+      <c r="D160" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E160" t="s">
+        <v>251</v>
+      </c>
+      <c r="F160" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="3">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>230</v>
+      </c>
+      <c r="C161" s="2">
+        <v>45826</v>
+      </c>
+      <c r="D161" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E161" t="s">
+        <v>176</v>
+      </c>
+      <c r="F161" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="3">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>230</v>
+      </c>
+      <c r="C162" s="2">
+        <v>45826</v>
+      </c>
+      <c r="D162" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E162" t="s">
+        <v>176</v>
+      </c>
+      <c r="F162" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="3">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>231</v>
+      </c>
+      <c r="C163" s="2">
+        <v>45831</v>
+      </c>
+      <c r="D163" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E163" t="s">
+        <v>75</v>
+      </c>
+      <c r="F163" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="3">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>232</v>
+      </c>
+      <c r="C164" s="2">
+        <v>45840</v>
+      </c>
+      <c r="D164" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E164" t="s">
+        <v>252</v>
+      </c>
+      <c r="F164" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="3">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>233</v>
+      </c>
+      <c r="C165" s="2">
+        <v>45877</v>
+      </c>
+      <c r="D165" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E165" t="s">
+        <v>101</v>
+      </c>
+      <c r="F165" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="3">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>234</v>
+      </c>
+      <c r="C166" s="2">
+        <v>45881</v>
+      </c>
+      <c r="D166" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E166" t="s">
+        <v>253</v>
+      </c>
+      <c r="F166" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="3">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>235</v>
+      </c>
+      <c r="C167" s="2">
+        <v>45884</v>
+      </c>
+      <c r="D167" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E167" t="s">
+        <v>186</v>
+      </c>
+      <c r="F167" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="3">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>236</v>
+      </c>
+      <c r="C168" s="2">
+        <v>45909</v>
+      </c>
+      <c r="D168" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E168" t="s">
+        <v>85</v>
+      </c>
+      <c r="F168" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="3">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>50</v>
+      </c>
+      <c r="C169" s="2">
+        <v>45925</v>
+      </c>
+      <c r="D169" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E169" t="s">
+        <v>77</v>
+      </c>
+      <c r="F169" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="3">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>237</v>
+      </c>
+      <c r="C170" s="2">
+        <v>45937</v>
+      </c>
+      <c r="D170" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E170" t="s">
+        <v>101</v>
+      </c>
+      <c r="F170" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="3">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>238</v>
+      </c>
+      <c r="C171" s="2">
+        <v>45947</v>
+      </c>
+      <c r="D171" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E171" t="s">
+        <v>80</v>
+      </c>
+      <c r="F171" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="3">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>239</v>
+      </c>
+      <c r="C172" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D172" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E172" t="s">
+        <v>254</v>
+      </c>
+      <c r="F172" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="3">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>240</v>
+      </c>
+      <c r="C173" s="2">
+        <v>45974</v>
+      </c>
+      <c r="D173" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E173" t="s">
+        <v>255</v>
+      </c>
+      <c r="F173" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="3">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>140</v>
+      </c>
+      <c r="C174" s="2">
+        <v>45979</v>
+      </c>
+      <c r="D174" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E174" t="s">
+        <v>146</v>
+      </c>
+      <c r="F174" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="3">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>241</v>
+      </c>
+      <c r="C175" s="2">
+        <v>45979</v>
+      </c>
+      <c r="D175" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E175" t="s">
+        <v>256</v>
+      </c>
+      <c r="F175" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="3">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>242</v>
+      </c>
+      <c r="C176" s="2">
+        <v>45980</v>
+      </c>
+      <c r="D176" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E176" t="s">
+        <v>257</v>
+      </c>
+      <c r="F176" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="3">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>204</v>
+      </c>
+      <c r="C177" s="2">
+        <v>45986</v>
+      </c>
+      <c r="D177" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E177" t="s">
+        <v>220</v>
+      </c>
+      <c r="F177" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="3">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>243</v>
+      </c>
+      <c r="C178" s="2">
+        <v>45986</v>
+      </c>
+      <c r="D178" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E178" t="s">
+        <v>258</v>
+      </c>
+      <c r="F178" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="3">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>48</v>
+      </c>
+      <c r="C179" s="2">
+        <v>46006</v>
+      </c>
+      <c r="D179" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E179" t="s">
+        <v>75</v>
+      </c>
+      <c r="F179" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="3">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>244</v>
+      </c>
+      <c r="C180" s="2">
+        <v>46010</v>
+      </c>
+      <c r="D180" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E180" t="s">
+        <v>259</v>
+      </c>
+      <c r="F180" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="3">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>237</v>
+      </c>
+      <c r="C181" s="2">
+        <v>46010</v>
+      </c>
+      <c r="D181" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E181" t="s">
+        <v>101</v>
+      </c>
+      <c r="F181" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="3">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>245</v>
+      </c>
+      <c r="C182" s="2">
+        <v>46014</v>
+      </c>
+      <c r="D182" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E182" t="s">
+        <v>260</v>
+      </c>
+      <c r="F182" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
